--- a/notebooks/Ale/feature_importance_theory.xlsx
+++ b/notebooks/Ale/feature_importance_theory.xlsx
@@ -505,77 +505,65 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2553</v>
+        <v>0.2418</v>
       </c>
       <c r="C4" t="n">
-        <v>0.209</v>
+        <v>0.3559</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1485</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.149</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.1464</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3331</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1147</v>
+          <t>broadband</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>0.091</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0243</v>
+        <v>0.0504</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.06710000000000001</v>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0271</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1048</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2928</v>
+        <v>0.08840000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0953</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1389</v>
+          <t>gcse_age19</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1198</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +573,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2009</v>
+        <v>0.1552</v>
       </c>
     </row>
     <row r="10">
@@ -594,126 +582,135 @@
           <t>nvq_level3</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.0428</v>
+      </c>
       <c r="C10" t="n">
-        <v>0.0452</v>
+        <v>0.0347</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1305</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2785</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0736</v>
+        <v>0.3895</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1373</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0871</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CLASSIFICATION</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>gd_emp_binary</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>gd_bus_binary</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.1907</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.0946</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0746</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.2391</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2411</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.09039999999999999</v>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.08169999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1043</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2144</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>drive_to_employer</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0712</v>
+        <v>0.0699</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.06909999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.096</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="20">
@@ -722,59 +719,62 @@
           <t>gcse_age19</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0.0678</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.0477</v>
-      </c>
       <c r="E20" t="n">
-        <v>0.109</v>
+        <v>0.0868</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1077</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2378</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0809</v>
+        <v>0.2688</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1293</v>
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0885</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.094</v>
+        <v>0.0861</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1731</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1404</v>
+        <v>0.0964</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1429</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -844,59 +844,56 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.322</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3065</v>
+        <v>0.6246</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.2578</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4402</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.074</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2191</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.2879</v>
+          <t>enterprise_death_rate</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1717</v>
       </c>
     </row>
     <row r="9">
@@ -905,14 +902,11 @@
           <t>fe_participation</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0.0351</v>
-      </c>
       <c r="D9" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1161</v>
       </c>
       <c r="E9" t="n">
-        <v>0.226</v>
+        <v>0.1583</v>
       </c>
     </row>
     <row r="10">
@@ -922,13 +916,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0357</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.059</v>
+        <v>0.0483</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1004</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="11">
@@ -938,203 +929,240 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1422</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1953</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1193</v>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0818</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1419</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1748</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CLASSIFICATION</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>gd_emp_binary</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>gd_bus_binary</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.1396</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.195</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.1913</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.3319</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0814</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1554</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0384</v>
+        <v>0.2591</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.127</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1051</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.1002</v>
+        <v>0.0954</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1085</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0823</v>
+          <t>drive_to_employer</t>
+        </is>
       </c>
       <c r="E22" t="n">
-        <v>0.1065</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.1303</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.1164</v>
+          <t>enterprise_birth_rate</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>0.0814</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1446</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.1393</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.1723</v>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1101</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0944</v>
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2177</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1686</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0781</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1203,113 +1231,113 @@
           <t>apprenticeship_achievements</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2374</v>
+      </c>
       <c r="D4" t="n">
-        <v>0.0741</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0847</v>
+        <v>0.1706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2684</v>
+        <v>0.3636</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1246</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.3637</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1231</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.074</v>
+        <v>0.0767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0613</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.101</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1082</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2626</v>
+        <v>0.1374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1117</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0897</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.07489999999999999</v>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1027</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.455</v>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0464</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1827</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="15">
@@ -1353,39 +1381,36 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1081</v>
+        <v>0.135</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1018</v>
+        <v>0.1401</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.15</v>
+        <v>0.1286</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0804</v>
+        <v>0.08359999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broadband</t>
+          <t>drive_to_employer</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.1326</v>
+        <v>0.0767</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1395,70 +1420,73 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.07630000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.082</v>
+        <v>0.2489</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.3047</v>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.0935</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1244</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0965</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.1799</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.1147</v>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -1476,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1533,21 +1561,21 @@
           <t>apprenticeship_achievements</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0.0515</v>
+      </c>
       <c r="C4" t="n">
-        <v>0.1918</v>
+        <v>0.3708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2724</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1249</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="6">
@@ -1557,65 +1585,62 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0843</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2461</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0536</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3322</v>
+        <v>0.0371</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2321</v>
+        <v>0.1891</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.062</v>
+        <v>0.1433</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06469999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2325</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.06759999999999999</v>
+          <t>housing_net_additions</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0881</v>
+        <v>0.1253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1537</v>
+        <v>0.2291</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3534</v>
       </c>
     </row>
     <row r="11">
@@ -1625,29 +1650,32 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3423</v>
+        <v>0.1767</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2596</v>
+        <v>0.29</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0822</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1082</v>
+        <v>0.4584</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0761</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.2648</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="14">
@@ -1690,121 +1718,128 @@
           <t>apprenticeship_achievements</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.0669</v>
+      </c>
       <c r="C16" t="n">
-        <v>0.1477</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.08</v>
+          <t>cycle_to_employer</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0922</v>
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0759</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.08550000000000001</v>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0876</v>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0606</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
-        </is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1546</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.1429</v>
+          <t>housing_net_additions</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1506</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.1427</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1045</v>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.074</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1693</v>
+        <v>0.1225</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1199</v>
+        <v>0.2226</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.2184</v>
+        <v>0.206</v>
       </c>
       <c r="D24" t="n">
-        <v>0.097</v>
+        <v>0.1734</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.09429999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1876,301 +1911,301 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0463</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0564</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0949</v>
+        <v>0.0793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0388</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1216</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0747</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coverage_4g</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0603</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08110000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1832</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.3185</v>
+          <t>gcse_age19</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3752</v>
+        <v>0.0649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1892</v>
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0853</v>
+          <t>housing_net_additions</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0905</v>
+        <v>0.0901</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09669999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0755</v>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.06660000000000001</v>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.2151</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0767</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.3526</v>
+        <v>0.0535</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1268</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0649</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0852</v>
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.0907</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.08019999999999999</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1006</v>
+          <t>enterprise_birth_rate</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>0.107</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.08690000000000001</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1763</v>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0848</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0852</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.1223</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.2263</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.2385</v>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0925</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1072</v>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1005</v>
+        <v>0.1879</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1223</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1134</v>
+        <v>0.0639</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1015</v>
+        <v>0.094</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1746</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0973</v>
+        <v>0.0839</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0969</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2236,24 +2271,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0424</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.1108</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.077</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1274</v>
       </c>
     </row>
     <row r="6">
@@ -2263,267 +2298,267 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0934</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1511</v>
       </c>
       <c r="C7" t="n">
-        <v>0.174</v>
+        <v>0.4286</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1086</v>
+        <v>0.1237</v>
       </c>
       <c r="E7" t="n">
-        <v>0.384</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2008</v>
+        <v>0.1192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3355</v>
+        <v>0.0224</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1328</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.1647</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0195</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1175</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1255</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1458</v>
+        <v>0.1117</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2536</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.113</v>
+        <v>0.1971</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1697</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1184</v>
+        <v>0.2777</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1055</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1754</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.2067</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.075</v>
+        <v>0.0832</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.0746</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0994</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.144</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.08169999999999999</v>
+          <t>drive_to_employer</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1581</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0842</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1327</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1302</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2274</v>
+        <v>0.0851</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1091</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1521</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1701</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1006</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0842</v>
+        <v>0.0882</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.073</v>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0602</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0856</v>
+        <v>0.127</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2168</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1217</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.1283</v>
+        <v>0.2712</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.146</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.1644</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.1299</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0844</v>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0868</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2535,7 +2570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2592,270 +2627,312 @@
           <t>apprenticeship_achievements</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0.0667</v>
+      </c>
       <c r="C4" t="n">
-        <v>0.0513</v>
+        <v>0.1467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.2286</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2665</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1537</v>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
-        </is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0442</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1034</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.07969999999999999</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1447</v>
+          <t>drive_to_employer</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>0.135</v>
+        <v>0.1028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.2639</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0403</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1612</v>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0924</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0949</v>
+        <v>0.1406</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1637</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1434</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1027</v>
+        <v>0.0733</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0827</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1507</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1324</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>nvq_level3</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4169</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1344</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.1074</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1136</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1062</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.1741</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.1933</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0828</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.1062</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.08890000000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.1194</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1399</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2207</v>
+        <v>0.0961</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1657</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.08740000000000001</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.09370000000000001</v>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.1745</v>
+          <t>drive_to_employer</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>0.2068</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.1653</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1058</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0858</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>nvq_level3</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0.1186</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.2456</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.09379999999999999</v>
+      <c r="B26" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1469</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0872</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
